--- a/halumem_experiment/experiment_results.xlsx
+++ b/halumem_experiment/experiment_results.xlsx
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5040,6 +5040,814 @@
       <c r="AF42" s="14" t="n"/>
       <c r="AG42" s="14" t="n"/>
     </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>amem-amem_cost_u34</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>A-MEM</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>10489125</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="L43" s="10" t="n">
+        <v>0.9823279924599434</v>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v>0.915475689424854</v>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v>0.1269230769230769</v>
+      </c>
+      <c r="O43" s="10" t="n">
+        <v>0.7754457050243112</v>
+      </c>
+      <c r="P43" s="10" t="n">
+        <v>0.8060200668896321</v>
+      </c>
+      <c r="Q43" s="10" t="n">
+        <v>0.1337792642140468</v>
+      </c>
+      <c r="R43" s="10" t="n">
+        <v>0.01337792642140468</v>
+      </c>
+      <c r="S43" s="10" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="T43" s="10" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="U43" s="10" t="n">
+        <v>0.3277777777777778</v>
+      </c>
+      <c r="V43" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA43" s="11" t="n"/>
+      <c r="AB43" s="11" t="n"/>
+      <c r="AC43" s="11" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="11" t="n"/>
+      <c r="AG43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>letta-letta_cost_u2</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Letta</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>openai-proxy/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>6101196</v>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>0.7369477911646586</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>0.9883268482490273</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.8443238787922703</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.3129251700680272</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>0.06270491803278688</v>
+      </c>
+      <c r="P44" s="13" t="n">
+        <v>0.654320987654321</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>0.2407407407407407</v>
+      </c>
+      <c r="R44" s="13" t="n">
+        <v>0.04938271604938271</v>
+      </c>
+      <c r="S44" s="13" t="n">
+        <v>0.5638297872340425</v>
+      </c>
+      <c r="T44" s="13" t="n">
+        <v>0.3829787234042553</v>
+      </c>
+      <c r="U44" s="13" t="n">
+        <v>0.05319148936170213</v>
+      </c>
+      <c r="V44" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="W44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="13" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="AA44" s="14" t="n"/>
+      <c r="AB44" s="14" t="n"/>
+      <c r="AC44" s="14" t="n"/>
+      <c r="AD44" s="14" t="n"/>
+      <c r="AE44" s="14" t="n"/>
+      <c r="AF44" s="14" t="n"/>
+      <c r="AG44" s="14" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>letta-letta_cost_u34</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Letta</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>openai-proxy/gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>11280670</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>0.6962962962962963</v>
+      </c>
+      <c r="L45" s="10" t="n">
+        <v>0.9953416149068323</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>0.8193865547932631</v>
+      </c>
+      <c r="N45" s="10" t="n">
+        <v>0.3423076923076923</v>
+      </c>
+      <c r="O45" s="10" t="n">
+        <v>0.07582116788321168</v>
+      </c>
+      <c r="P45" s="10" t="n">
+        <v>0.5852842809364549</v>
+      </c>
+      <c r="Q45" s="10" t="n">
+        <v>0.2709030100334448</v>
+      </c>
+      <c r="R45" s="10" t="n">
+        <v>0.03010033444816054</v>
+      </c>
+      <c r="S45" s="10" t="n">
+        <v>0.5055555555555555</v>
+      </c>
+      <c r="T45" s="10" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="U45" s="10" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="W45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="10" t="n">
+        <v>0.7471910112359551</v>
+      </c>
+      <c r="AA45" s="11" t="n"/>
+      <c r="AB45" s="11" t="n"/>
+      <c r="AC45" s="11" t="n"/>
+      <c r="AD45" s="11" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="11" t="n"/>
+      <c r="AG45" s="11" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>5117424</v>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>0.8802660753880266</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>0.9945395879870935</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>0.9339202212130908</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>0.8547133138969873</v>
+      </c>
+      <c r="P46" s="13" t="n">
+        <v>0.7183098591549296</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>0.08450704225352113</v>
+      </c>
+      <c r="R46" s="13" t="n">
+        <v>0.01408450704225352</v>
+      </c>
+      <c r="S46" s="13" t="n">
+        <v>0.5304878048780488</v>
+      </c>
+      <c r="T46" s="13" t="n">
+        <v>0.1402439024390244</v>
+      </c>
+      <c r="U46" s="13" t="n">
+        <v>0.3292682926829268</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="W46" s="13" t="n">
+        <v>0.2428571428571429</v>
+      </c>
+      <c r="X46" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y46" s="13" t="n">
+        <v>0.4571428571428571</v>
+      </c>
+      <c r="Z46" s="13" t="n">
+        <v>0.05194805194805195</v>
+      </c>
+      <c r="AA46" s="14" t="n"/>
+      <c r="AB46" s="14" t="n"/>
+      <c r="AC46" s="14" t="n"/>
+      <c r="AD46" s="14" t="n"/>
+      <c r="AE46" s="14" t="n"/>
+      <c r="AF46" s="14" t="n"/>
+      <c r="AG46" s="14" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>3201363</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>0.844789356984479</v>
+      </c>
+      <c r="L47" s="10" t="n">
+        <v>0.9960810810810811</v>
+      </c>
+      <c r="M47" s="10" t="n">
+        <v>0.9142182726071058</v>
+      </c>
+      <c r="N47" s="10" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="O47" s="10" t="n">
+        <v>0.8396420489611192</v>
+      </c>
+      <c r="P47" s="10" t="n">
+        <v>0.7394366197183099</v>
+      </c>
+      <c r="Q47" s="10" t="n">
+        <v>0.09154929577464789</v>
+      </c>
+      <c r="R47" s="10" t="n">
+        <v>0.007042253521126761</v>
+      </c>
+      <c r="S47" s="10" t="n">
+        <v>0.4573170731707317</v>
+      </c>
+      <c r="T47" s="10" t="n">
+        <v>0.1707317073170732</v>
+      </c>
+      <c r="U47" s="10" t="n">
+        <v>0.3719512195121951</v>
+      </c>
+      <c r="V47" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="W47" s="10" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+      <c r="X47" s="10" t="n">
+        <v>0.345679012345679</v>
+      </c>
+      <c r="Y47" s="10" t="n">
+        <v>0.3950617283950617</v>
+      </c>
+      <c r="Z47" s="10" t="n">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="AA47" s="11" t="n"/>
+      <c r="AB47" s="11" t="n"/>
+      <c r="AC47" s="11" t="n"/>
+      <c r="AD47" s="11" t="n"/>
+      <c r="AE47" s="11" t="n"/>
+      <c r="AF47" s="11" t="n"/>
+      <c r="AG47" s="11" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>3435712</v>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>0.9024390243902439</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>0.9961129826379891</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.946965081711259</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>0.8439433246856914</v>
+      </c>
+      <c r="P48" s="13" t="n">
+        <v>0.6408450704225352</v>
+      </c>
+      <c r="Q48" s="13" t="n">
+        <v>0.1197183098591549</v>
+      </c>
+      <c r="R48" s="13" t="n">
+        <v>0.007042253521126761</v>
+      </c>
+      <c r="S48" s="13" t="n">
+        <v>0.4695121951219512</v>
+      </c>
+      <c r="T48" s="13" t="n">
+        <v>0.1829268292682927</v>
+      </c>
+      <c r="U48" s="13" t="n">
+        <v>0.3475609756097561</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="W48" s="13" t="n">
+        <v>0.2151898734177215</v>
+      </c>
+      <c r="X48" s="13" t="n">
+        <v>0.379746835443038</v>
+      </c>
+      <c r="Y48" s="13" t="n">
+        <v>0.4050632911392405</v>
+      </c>
+      <c r="Z48" s="13" t="n">
+        <v>0.01149425287356322</v>
+      </c>
+      <c r="AA48" s="14" t="n"/>
+      <c r="AB48" s="14" t="n"/>
+      <c r="AC48" s="14" t="n"/>
+      <c r="AD48" s="14" t="n"/>
+      <c r="AE48" s="14" t="n"/>
+      <c r="AF48" s="14" t="n"/>
+      <c r="AG48" s="14" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>3333726</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>0.8736141906873615</v>
+      </c>
+      <c r="L49" s="10" t="n">
+        <v>0.9960306959513099</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>0.9308147836647847</v>
+      </c>
+      <c r="N49" s="10" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="O49" s="10" t="n">
+        <v>0.842386914378029</v>
+      </c>
+      <c r="P49" s="10" t="n">
+        <v>0.7112676056338029</v>
+      </c>
+      <c r="Q49" s="10" t="n">
+        <v>0.09859154929577464</v>
+      </c>
+      <c r="R49" s="10" t="n">
+        <v>0.01408450704225352</v>
+      </c>
+      <c r="S49" s="10" t="n">
+        <v>0.4939024390243902</v>
+      </c>
+      <c r="T49" s="10" t="n">
+        <v>0.1524390243902439</v>
+      </c>
+      <c r="U49" s="10" t="n">
+        <v>0.3536585365853658</v>
+      </c>
+      <c r="V49" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="W49" s="10" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="X49" s="10" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="Y49" s="10" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="Z49" s="10" t="n">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="AA49" s="11" t="n"/>
+      <c r="AB49" s="11" t="n"/>
+      <c r="AC49" s="11" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+      <c r="AE49" s="11" t="n"/>
+      <c r="AF49" s="11" t="n"/>
+      <c r="AG49" s="11" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>mxbai-embed-large</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>HaluMem-Medium</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>3663843</v>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>0.8802660753880266</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>0.9968290208016235</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.9349284133288044</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>0.8318890814558059</v>
+      </c>
+      <c r="P50" s="13" t="n">
+        <v>0.7253521126760564</v>
+      </c>
+      <c r="Q50" s="13" t="n">
+        <v>0.09859154929577464</v>
+      </c>
+      <c r="R50" s="13" t="n">
+        <v>0.007042253521126761</v>
+      </c>
+      <c r="S50" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T50" s="13" t="n">
+        <v>0.1646341463414634</v>
+      </c>
+      <c r="U50" s="13" t="n">
+        <v>0.3353658536585366</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="W50" s="13" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="X50" s="13" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="Y50" s="13" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Z50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="14" t="n"/>
+      <c r="AB50" s="14" t="n"/>
+      <c r="AC50" s="14" t="n"/>
+      <c r="AD50" s="14" t="n"/>
+      <c r="AE50" s="14" t="n"/>
+      <c r="AF50" s="14" t="n"/>
+      <c r="AG50" s="14" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
